--- a/dist/xlsx/cities.xlsx
+++ b/dist/xlsx/cities.xlsx
@@ -22601,33 +22601,33 @@
     </row>
     <row r="1111">
       <c r="A1111">
-        <v>10300010002401</v>
+        <v>10300010002144</v>
       </c>
       <c r="B1111" t="str">
-        <v>آقکند</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="C1111" t="str">
-        <v>آقکند</v>
+        <v>ترکمانچای</v>
       </c>
       <c r="D1111">
         <v>103</v>
       </c>
       <c r="E1111">
-        <v>10300010</v>
+        <v>10300029</v>
       </c>
       <c r="F1111">
-        <v>10300010002</v>
+        <v>10300029001</v>
       </c>
     </row>
     <row r="1112">
       <c r="A1112">
-        <v>10300010002402</v>
+        <v>10300010002401</v>
       </c>
       <c r="B1112" t="str">
-        <v>ترک</v>
+        <v>آقکند</v>
       </c>
       <c r="C1112" t="str">
-        <v>ترک</v>
+        <v>آقکند</v>
       </c>
       <c r="D1112">
         <v>103</v>
@@ -22636,18 +22636,18 @@
         <v>10300010</v>
       </c>
       <c r="F1112">
-        <v>10300010003</v>
+        <v>10300010002</v>
       </c>
     </row>
     <row r="1113">
       <c r="A1113">
-        <v>10300010002842</v>
+        <v>10300010002402</v>
       </c>
       <c r="B1113" t="str">
-        <v>اچاچی</v>
+        <v>ترک</v>
       </c>
       <c r="C1113" t="str">
-        <v>اچاچی</v>
+        <v>ترک</v>
       </c>
       <c r="D1113">
         <v>103</v>
@@ -22656,38 +22656,38 @@
         <v>10300010</v>
       </c>
       <c r="F1113">
-        <v>10300010004</v>
+        <v>10300010003</v>
       </c>
     </row>
     <row r="1114">
       <c r="A1114">
-        <v>10300011001234</v>
+        <v>10300010002842</v>
       </c>
       <c r="B1114" t="str">
-        <v>هشترود</v>
+        <v>اچاچی</v>
       </c>
       <c r="C1114" t="str">
-        <v>هشترود</v>
+        <v>اچاچی</v>
       </c>
       <c r="D1114">
         <v>103</v>
       </c>
       <c r="E1114">
-        <v>10300011</v>
+        <v>10300010</v>
       </c>
       <c r="F1114">
-        <v>10300011002</v>
+        <v>10300010004</v>
       </c>
     </row>
     <row r="1115">
       <c r="A1115">
-        <v>10300011002590</v>
+        <v>10300011001234</v>
       </c>
       <c r="B1115" t="str">
-        <v>نظرکهریزی</v>
+        <v>هشترود</v>
       </c>
       <c r="C1115" t="str">
-        <v>نظرکهریزی</v>
+        <v>هشترود</v>
       </c>
       <c r="D1115">
         <v>103</v>
@@ -22696,38 +22696,38 @@
         <v>10300011</v>
       </c>
       <c r="F1115">
-        <v>10300011003</v>
+        <v>10300011002</v>
       </c>
     </row>
     <row r="1116">
       <c r="A1116">
-        <v>10300012001221</v>
+        <v>10300011002590</v>
       </c>
       <c r="B1116" t="str">
-        <v>بناب</v>
+        <v>نظرکهریزی</v>
       </c>
       <c r="C1116" t="str">
-        <v>بناب</v>
+        <v>نظرکهریزی</v>
       </c>
       <c r="D1116">
         <v>103</v>
       </c>
       <c r="E1116">
-        <v>10300012</v>
+        <v>10300011</v>
       </c>
       <c r="F1116">
-        <v>10300012001</v>
+        <v>10300011003</v>
       </c>
     </row>
     <row r="1117">
       <c r="A1117">
-        <v>10300012002934</v>
+        <v>10300012001221</v>
       </c>
       <c r="B1117" t="str">
-        <v>خوشه مهر</v>
+        <v>بناب</v>
       </c>
       <c r="C1117" t="str">
-        <v>خوشه-مهر</v>
+        <v>بناب</v>
       </c>
       <c r="D1117">
         <v>103</v>
@@ -22741,33 +22741,33 @@
     </row>
     <row r="1118">
       <c r="A1118">
-        <v>10300013001025</v>
+        <v>10300012002934</v>
       </c>
       <c r="B1118" t="str">
-        <v>کردکندی</v>
+        <v>خوشه مهر</v>
       </c>
       <c r="C1118" t="str">
-        <v>کردکندی</v>
+        <v>خوشه-مهر</v>
       </c>
       <c r="D1118">
         <v>103</v>
       </c>
       <c r="E1118">
-        <v>10300013</v>
+        <v>10300012</v>
       </c>
       <c r="F1118">
-        <v>10300013002</v>
+        <v>10300012001</v>
       </c>
     </row>
     <row r="1119">
       <c r="A1119">
-        <v>10300013001207</v>
+        <v>10300013001025</v>
       </c>
       <c r="B1119" t="str">
-        <v>بستان آباد</v>
+        <v>کردکندی</v>
       </c>
       <c r="C1119" t="str">
-        <v>بستان-آباد</v>
+        <v>کردکندی</v>
       </c>
       <c r="D1119">
         <v>103</v>
@@ -22781,13 +22781,13 @@
     </row>
     <row r="1120">
       <c r="A1120">
-        <v>10300013002295</v>
+        <v>10300013001207</v>
       </c>
       <c r="B1120" t="str">
-        <v>تیکمه داش</v>
+        <v>بستان آباد</v>
       </c>
       <c r="C1120" t="str">
-        <v>تیکمه-داش</v>
+        <v>بستان-آباد</v>
       </c>
       <c r="D1120">
         <v>103</v>
@@ -22796,38 +22796,38 @@
         <v>10300013</v>
       </c>
       <c r="F1120">
-        <v>10300013001</v>
+        <v>10300013002</v>
       </c>
     </row>
     <row r="1121">
       <c r="A1121">
-        <v>10300014001083</v>
+        <v>10300013002295</v>
       </c>
       <c r="B1121" t="str">
-        <v>نظرلو</v>
+        <v>تیکمه داش</v>
       </c>
       <c r="C1121" t="str">
-        <v>نظرلو</v>
+        <v>تیکمه-داش</v>
       </c>
       <c r="D1121">
         <v>103</v>
       </c>
       <c r="E1121">
-        <v>10300014</v>
+        <v>10300013</v>
       </c>
       <c r="F1121">
-        <v>10300014001</v>
+        <v>10300013001</v>
       </c>
     </row>
     <row r="1122">
       <c r="A1122">
-        <v>10300014001208</v>
+        <v>10300014001083</v>
       </c>
       <c r="B1122" t="str">
-        <v>تسوج</v>
+        <v>نظرلو</v>
       </c>
       <c r="C1122" t="str">
-        <v>تسوج</v>
+        <v>نظرلو</v>
       </c>
       <c r="D1122">
         <v>103</v>
@@ -22836,18 +22836,18 @@
         <v>10300014</v>
       </c>
       <c r="F1122">
-        <v>10300014003</v>
+        <v>10300014001</v>
       </c>
     </row>
     <row r="1123">
       <c r="A1123">
-        <v>10300014001209</v>
+        <v>10300014001208</v>
       </c>
       <c r="B1123" t="str">
-        <v>خامنه</v>
+        <v>تسوج</v>
       </c>
       <c r="C1123" t="str">
-        <v>خامنه</v>
+        <v>تسوج</v>
       </c>
       <c r="D1123">
         <v>103</v>
@@ -22856,18 +22856,18 @@
         <v>10300014</v>
       </c>
       <c r="F1123">
-        <v>10300014002</v>
+        <v>10300014003</v>
       </c>
     </row>
     <row r="1124">
       <c r="A1124">
-        <v>10300014001210</v>
+        <v>10300014001209</v>
       </c>
       <c r="B1124" t="str">
-        <v>شبستر</v>
+        <v>خامنه</v>
       </c>
       <c r="C1124" t="str">
-        <v>شبستر</v>
+        <v>خامنه</v>
       </c>
       <c r="D1124">
         <v>103</v>
@@ -22881,13 +22881,13 @@
     </row>
     <row r="1125">
       <c r="A1125">
-        <v>10300014001211</v>
+        <v>10300014001210</v>
       </c>
       <c r="B1125" t="str">
-        <v>شرفخانه</v>
+        <v>شبستر</v>
       </c>
       <c r="C1125" t="str">
-        <v>شرفخانه</v>
+        <v>شبستر</v>
       </c>
       <c r="D1125">
         <v>103</v>
@@ -22901,13 +22901,13 @@
     </row>
     <row r="1126">
       <c r="A1126">
-        <v>10300014001212</v>
+        <v>10300014001211</v>
       </c>
       <c r="B1126" t="str">
-        <v>صوفیان</v>
+        <v>شرفخانه</v>
       </c>
       <c r="C1126" t="str">
-        <v>صوفیان</v>
+        <v>شرفخانه</v>
       </c>
       <c r="D1126">
         <v>103</v>
@@ -22916,18 +22916,18 @@
         <v>10300014</v>
       </c>
       <c r="F1126">
-        <v>10300014001</v>
+        <v>10300014002</v>
       </c>
     </row>
     <row r="1127">
       <c r="A1127">
-        <v>10300014002101</v>
+        <v>10300014001212</v>
       </c>
       <c r="B1127" t="str">
-        <v>شندآباد</v>
+        <v>صوفیان</v>
       </c>
       <c r="C1127" t="str">
-        <v>شندآباد</v>
+        <v>صوفیان</v>
       </c>
       <c r="D1127">
         <v>103</v>
@@ -22936,18 +22936,18 @@
         <v>10300014</v>
       </c>
       <c r="F1127">
-        <v>10300014002</v>
+        <v>10300014001</v>
       </c>
     </row>
     <row r="1128">
       <c r="A1128">
-        <v>10300014002148</v>
+        <v>10300014002101</v>
       </c>
       <c r="B1128" t="str">
-        <v>سیس</v>
+        <v>شندآباد</v>
       </c>
       <c r="C1128" t="str">
-        <v>سیس</v>
+        <v>شندآباد</v>
       </c>
       <c r="D1128">
         <v>103</v>
@@ -22961,13 +22961,13 @@
     </row>
     <row r="1129">
       <c r="A1129">
-        <v>10300014002149</v>
+        <v>10300014002148</v>
       </c>
       <c r="B1129" t="str">
-        <v>وایقان</v>
+        <v>سیس</v>
       </c>
       <c r="C1129" t="str">
-        <v>وایقان</v>
+        <v>سیس</v>
       </c>
       <c r="D1129">
         <v>103</v>
@@ -22981,13 +22981,13 @@
     </row>
     <row r="1130">
       <c r="A1130">
-        <v>10300014002544</v>
+        <v>10300014002149</v>
       </c>
       <c r="B1130" t="str">
-        <v>کوزه کنان</v>
+        <v>وایقان</v>
       </c>
       <c r="C1130" t="str">
-        <v>کوزه-کنان</v>
+        <v>وایقان</v>
       </c>
       <c r="D1130">
         <v>103</v>
@@ -23001,13 +23001,13 @@
     </row>
     <row r="1131">
       <c r="A1131">
-        <v>10300014002946</v>
+        <v>10300014002544</v>
       </c>
       <c r="B1131" t="str">
-        <v>داریان</v>
+        <v>کوزه کنان</v>
       </c>
       <c r="C1131" t="str">
-        <v>داریان</v>
+        <v>کوزه-کنان</v>
       </c>
       <c r="D1131">
         <v>103</v>
@@ -23021,13 +23021,13 @@
     </row>
     <row r="1132">
       <c r="A1132">
-        <v>10300014002947</v>
+        <v>10300014002946</v>
       </c>
       <c r="B1132" t="str">
-        <v>علیشاه</v>
+        <v>داریان</v>
       </c>
       <c r="C1132" t="str">
-        <v>علیشاه</v>
+        <v>داریان</v>
       </c>
       <c r="D1132">
         <v>103</v>
@@ -23041,33 +23041,33 @@
     </row>
     <row r="1133">
       <c r="A1133">
-        <v>10300015001199</v>
+        <v>10300014002947</v>
       </c>
       <c r="B1133" t="str">
-        <v>کلیبر</v>
+        <v>علیشاه</v>
       </c>
       <c r="C1133" t="str">
-        <v>کلیبر</v>
+        <v>علیشاه</v>
       </c>
       <c r="D1133">
         <v>103</v>
       </c>
       <c r="E1133">
-        <v>10300015</v>
+        <v>10300014</v>
       </c>
       <c r="F1133">
-        <v>10300015002</v>
+        <v>10300014002</v>
       </c>
     </row>
     <row r="1134">
       <c r="A1134">
-        <v>10300015002545</v>
+        <v>10300015001199</v>
       </c>
       <c r="B1134" t="str">
-        <v>آبش احمد</v>
+        <v>کلیبر</v>
       </c>
       <c r="C1134" t="str">
-        <v>آبش-احمد</v>
+        <v>کلیبر</v>
       </c>
       <c r="D1134">
         <v>103</v>
@@ -23076,38 +23076,38 @@
         <v>10300015</v>
       </c>
       <c r="F1134">
-        <v>10300015003</v>
+        <v>10300015002</v>
       </c>
     </row>
     <row r="1135">
       <c r="A1135">
-        <v>10300016001217</v>
+        <v>10300015002545</v>
       </c>
       <c r="B1135" t="str">
-        <v>هریس</v>
+        <v>آبش احمد</v>
       </c>
       <c r="C1135" t="str">
-        <v>هریس</v>
+        <v>آبش-احمد</v>
       </c>
       <c r="D1135">
         <v>103</v>
       </c>
       <c r="E1135">
-        <v>10300016</v>
+        <v>10300015</v>
       </c>
       <c r="F1135">
-        <v>10300016002</v>
+        <v>10300015003</v>
       </c>
     </row>
     <row r="1136">
       <c r="A1136">
-        <v>10300016002146</v>
+        <v>10300016001217</v>
       </c>
       <c r="B1136" t="str">
-        <v>خواجه</v>
+        <v>هریس</v>
       </c>
       <c r="C1136" t="str">
-        <v>خواجه</v>
+        <v>هریس</v>
       </c>
       <c r="D1136">
         <v>103</v>
@@ -23116,18 +23116,18 @@
         <v>10300016</v>
       </c>
       <c r="F1136">
-        <v>10300016001</v>
+        <v>10300016002</v>
       </c>
     </row>
     <row r="1137">
       <c r="A1137">
-        <v>10300016002147</v>
+        <v>10300016002146</v>
       </c>
       <c r="B1137" t="str">
-        <v>زرنق</v>
+        <v>خواجه</v>
       </c>
       <c r="C1137" t="str">
-        <v>زرنق</v>
+        <v>خواجه</v>
       </c>
       <c r="D1137">
         <v>103</v>
@@ -23136,18 +23136,18 @@
         <v>10300016</v>
       </c>
       <c r="F1137">
-        <v>10300016002</v>
+        <v>10300016001</v>
       </c>
     </row>
     <row r="1138">
       <c r="A1138">
-        <v>10300016002230</v>
+        <v>10300016002147</v>
       </c>
       <c r="B1138" t="str">
-        <v>بخشایش</v>
+        <v>زرنق</v>
       </c>
       <c r="C1138" t="str">
-        <v>بخشایش</v>
+        <v>زرنق</v>
       </c>
       <c r="D1138">
         <v>103</v>
@@ -23161,13 +23161,13 @@
     </row>
     <row r="1139">
       <c r="A1139">
-        <v>10300016002333</v>
+        <v>10300016002230</v>
       </c>
       <c r="B1139" t="str">
-        <v>کلوانق</v>
+        <v>بخشایش</v>
       </c>
       <c r="C1139" t="str">
-        <v>کلوانق</v>
+        <v>بخشایش</v>
       </c>
       <c r="D1139">
         <v>103</v>
@@ -23181,13 +23181,13 @@
     </row>
     <row r="1140">
       <c r="A1140">
-        <v>10300016002935</v>
+        <v>10300016002333</v>
       </c>
       <c r="B1140" t="str">
-        <v>اربطان</v>
+        <v>کلوانق</v>
       </c>
       <c r="C1140" t="str">
-        <v>اربطان</v>
+        <v>کلوانق</v>
       </c>
       <c r="D1140">
         <v>103</v>
@@ -23196,38 +23196,38 @@
         <v>10300016</v>
       </c>
       <c r="F1140">
-        <v>10300016001</v>
+        <v>10300016002</v>
       </c>
     </row>
     <row r="1141">
       <c r="A1141">
-        <v>10300019001225</v>
+        <v>10300016002935</v>
       </c>
       <c r="B1141" t="str">
-        <v>جلفا</v>
+        <v>اربطان</v>
       </c>
       <c r="C1141" t="str">
-        <v>جلفا</v>
+        <v>اربطان</v>
       </c>
       <c r="D1141">
         <v>103</v>
       </c>
       <c r="E1141">
-        <v>10300019</v>
+        <v>10300016</v>
       </c>
       <c r="F1141">
-        <v>10300019002</v>
+        <v>10300016001</v>
       </c>
     </row>
     <row r="1142">
       <c r="A1142">
-        <v>10300019001226</v>
+        <v>10300019001225</v>
       </c>
       <c r="B1142" t="str">
-        <v>هادیشهر</v>
+        <v>جلفا</v>
       </c>
       <c r="C1142" t="str">
-        <v>هادیشهر</v>
+        <v>جلفا</v>
       </c>
       <c r="D1142">
         <v>103</v>
@@ -23241,13 +23241,13 @@
     </row>
     <row r="1143">
       <c r="A1143">
-        <v>10300019002497</v>
+        <v>10300019001226</v>
       </c>
       <c r="B1143" t="str">
-        <v>سیه رود</v>
+        <v>هادیشهر</v>
       </c>
       <c r="C1143" t="str">
-        <v>سیه-رود</v>
+        <v>هادیشهر</v>
       </c>
       <c r="D1143">
         <v>103</v>
@@ -23256,38 +23256,38 @@
         <v>10300019</v>
       </c>
       <c r="F1143">
-        <v>10300019001</v>
+        <v>10300019002</v>
       </c>
     </row>
     <row r="1144">
       <c r="A1144">
-        <v>10300020001224</v>
+        <v>10300019002497</v>
       </c>
       <c r="B1144" t="str">
-        <v>ملکان</v>
+        <v>سیه رود</v>
       </c>
       <c r="C1144" t="str">
-        <v>ملکان</v>
+        <v>سیه-رود</v>
       </c>
       <c r="D1144">
         <v>103</v>
       </c>
       <c r="E1144">
-        <v>10300020</v>
+        <v>10300019</v>
       </c>
       <c r="F1144">
-        <v>10300020002</v>
+        <v>10300019001</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145">
-        <v>10300020002844</v>
+        <v>10300020001224</v>
       </c>
       <c r="B1145" t="str">
-        <v>مبارک شهر</v>
+        <v>ملکان</v>
       </c>
       <c r="C1145" t="str">
-        <v>مبارک-شهر</v>
+        <v>ملکان</v>
       </c>
       <c r="D1145">
         <v>103</v>
@@ -23301,33 +23301,33 @@
     </row>
     <row r="1146">
       <c r="A1146">
-        <v>10300021001201</v>
+        <v>10300020002844</v>
       </c>
       <c r="B1146" t="str">
-        <v>آذرشهر</v>
+        <v>مبارک شهر</v>
       </c>
       <c r="C1146" t="str">
-        <v>آذرشهر</v>
+        <v>مبارک-شهر</v>
       </c>
       <c r="D1146">
         <v>103</v>
       </c>
       <c r="E1146">
-        <v>10300021</v>
+        <v>10300020</v>
       </c>
       <c r="F1146">
-        <v>10300021003</v>
+        <v>10300020002</v>
       </c>
     </row>
     <row r="1147">
       <c r="A1147">
-        <v>10300021001202</v>
+        <v>10300021001201</v>
       </c>
       <c r="B1147" t="str">
-        <v>گوگان</v>
+        <v>آذرشهر</v>
       </c>
       <c r="C1147" t="str">
-        <v>گوگان</v>
+        <v>آذرشهر</v>
       </c>
       <c r="D1147">
         <v>103</v>
@@ -23336,18 +23336,18 @@
         <v>10300021</v>
       </c>
       <c r="F1147">
-        <v>10300021001</v>
+        <v>10300021003</v>
       </c>
     </row>
     <row r="1148">
       <c r="A1148">
-        <v>10300021001203</v>
+        <v>10300021001202</v>
       </c>
       <c r="B1148" t="str">
-        <v>ممقان</v>
+        <v>گوگان</v>
       </c>
       <c r="C1148" t="str">
-        <v>ممقان</v>
+        <v>گوگان</v>
       </c>
       <c r="D1148">
         <v>103</v>
@@ -23356,18 +23356,18 @@
         <v>10300021</v>
       </c>
       <c r="F1148">
-        <v>10300021002</v>
+        <v>10300021001</v>
       </c>
     </row>
     <row r="1149">
       <c r="A1149">
-        <v>10300021002763</v>
+        <v>10300021001203</v>
       </c>
       <c r="B1149" t="str">
-        <v>تیمورلو</v>
+        <v>ممقان</v>
       </c>
       <c r="C1149" t="str">
-        <v>تیمورلو</v>
+        <v>ممقان</v>
       </c>
       <c r="D1149">
         <v>103</v>
@@ -23376,38 +23376,38 @@
         <v>10300021</v>
       </c>
       <c r="F1149">
-        <v>10300021001</v>
+        <v>10300021002</v>
       </c>
     </row>
     <row r="1150">
       <c r="A1150">
-        <v>10300022001204</v>
+        <v>10300021002763</v>
       </c>
       <c r="B1150" t="str">
-        <v>اسکو</v>
+        <v>تیمورلو</v>
       </c>
       <c r="C1150" t="str">
-        <v>اسکو</v>
+        <v>تیمورلو</v>
       </c>
       <c r="D1150">
         <v>103</v>
       </c>
       <c r="E1150">
-        <v>10300022</v>
+        <v>10300021</v>
       </c>
       <c r="F1150">
-        <v>10300022002</v>
+        <v>10300021001</v>
       </c>
     </row>
     <row r="1151">
       <c r="A1151">
-        <v>10300022001205</v>
+        <v>10300022001204</v>
       </c>
       <c r="B1151" t="str">
-        <v>ایلخچی</v>
+        <v>اسکو</v>
       </c>
       <c r="C1151" t="str">
-        <v>ایلخچی</v>
+        <v>اسکو</v>
       </c>
       <c r="D1151">
         <v>103</v>
@@ -23416,18 +23416,18 @@
         <v>10300022</v>
       </c>
       <c r="F1151">
-        <v>10300022001</v>
+        <v>10300022002</v>
       </c>
     </row>
     <row r="1152">
       <c r="A1152">
-        <v>10300022002033</v>
+        <v>10300022001205</v>
       </c>
       <c r="B1152" t="str">
-        <v>سهند</v>
+        <v>ایلخچی</v>
       </c>
       <c r="C1152" t="str">
-        <v>سهند</v>
+        <v>ایلخچی</v>
       </c>
       <c r="D1152">
         <v>103</v>
@@ -23436,58 +23436,58 @@
         <v>10300022</v>
       </c>
       <c r="F1152">
-        <v>10300022002</v>
+        <v>10300022001</v>
       </c>
     </row>
     <row r="1153">
       <c r="A1153">
-        <v>10300023002145</v>
+        <v>10300022002033</v>
       </c>
       <c r="B1153" t="str">
-        <v>قره آغاج</v>
+        <v>سهند</v>
       </c>
       <c r="C1153" t="str">
-        <v>قره-آغاج</v>
+        <v>سهند</v>
       </c>
       <c r="D1153">
         <v>103</v>
       </c>
       <c r="E1153">
-        <v>10300023</v>
+        <v>10300022</v>
       </c>
       <c r="F1153">
-        <v>10300023002</v>
+        <v>10300022002</v>
       </c>
     </row>
     <row r="1154">
       <c r="A1154">
-        <v>10300024002142</v>
+        <v>10300023002145</v>
       </c>
       <c r="B1154" t="str">
-        <v>ورزقان</v>
+        <v>قره آغاج</v>
       </c>
       <c r="C1154" t="str">
-        <v>ورزقان</v>
+        <v>قره-آغاج</v>
       </c>
       <c r="D1154">
         <v>103</v>
       </c>
       <c r="E1154">
-        <v>10300024</v>
+        <v>10300023</v>
       </c>
       <c r="F1154">
-        <v>10300024002</v>
+        <v>10300023002</v>
       </c>
     </row>
     <row r="1155">
       <c r="A1155">
-        <v>10300024002398</v>
+        <v>10300024002142</v>
       </c>
       <c r="B1155" t="str">
-        <v>خاروانا</v>
+        <v>ورزقان</v>
       </c>
       <c r="C1155" t="str">
-        <v>خاروانا</v>
+        <v>ورزقان</v>
       </c>
       <c r="D1155">
         <v>103</v>
@@ -23496,38 +23496,38 @@
         <v>10300024</v>
       </c>
       <c r="F1155">
-        <v>10300024001</v>
+        <v>10300024002</v>
       </c>
     </row>
     <row r="1156">
       <c r="A1156">
-        <v>10300025001222</v>
+        <v>10300024002398</v>
       </c>
       <c r="B1156" t="str">
-        <v>عجب شیر</v>
+        <v>خاروانا</v>
       </c>
       <c r="C1156" t="str">
-        <v>عجب-شیر</v>
+        <v>خاروانا</v>
       </c>
       <c r="D1156">
         <v>103</v>
       </c>
       <c r="E1156">
-        <v>10300025</v>
+        <v>10300024</v>
       </c>
       <c r="F1156">
-        <v>10300025002</v>
+        <v>10300024001</v>
       </c>
     </row>
     <row r="1157">
       <c r="A1157">
-        <v>10300025002843</v>
+        <v>10300025001222</v>
       </c>
       <c r="B1157" t="str">
-        <v>جوان قلعه</v>
+        <v>عجب شیر</v>
       </c>
       <c r="C1157" t="str">
-        <v>جوان-قلعه</v>
+        <v>عجب-شیر</v>
       </c>
       <c r="D1157">
         <v>103</v>
@@ -23536,38 +23536,38 @@
         <v>10300025</v>
       </c>
       <c r="F1157">
-        <v>10300025001</v>
+        <v>10300025002</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158">
-        <v>10300026002332</v>
+        <v>10300025002843</v>
       </c>
       <c r="B1158" t="str">
-        <v>خمارلو</v>
+        <v>جوان قلعه</v>
       </c>
       <c r="C1158" t="str">
-        <v>خمارلو</v>
+        <v>جوان-قلعه</v>
       </c>
       <c r="D1158">
         <v>103</v>
       </c>
       <c r="E1158">
-        <v>10300026</v>
+        <v>10300025</v>
       </c>
       <c r="F1158">
-        <v>10300026001</v>
+        <v>10300025001</v>
       </c>
     </row>
     <row r="1159">
       <c r="A1159">
-        <v>10300026002944</v>
+        <v>10300026002332</v>
       </c>
       <c r="B1159" t="str">
-        <v>عاشقلو</v>
+        <v>خمارلو</v>
       </c>
       <c r="C1159" t="str">
-        <v>عاشقلو</v>
+        <v>خمارلو</v>
       </c>
       <c r="D1159">
         <v>103</v>
@@ -23576,18 +23576,18 @@
         <v>10300026</v>
       </c>
       <c r="F1159">
-        <v>10300026003</v>
+        <v>10300026001</v>
       </c>
     </row>
     <row r="1160">
       <c r="A1160">
-        <v>10300026002945</v>
+        <v>10300026002944</v>
       </c>
       <c r="B1160" t="str">
-        <v>لاریجان</v>
+        <v>عاشقلو</v>
       </c>
       <c r="C1160" t="str">
-        <v>لاریجان</v>
+        <v>عاشقلو</v>
       </c>
       <c r="D1160">
         <v>103</v>
@@ -23596,67 +23596,67 @@
         <v>10300026</v>
       </c>
       <c r="F1160">
-        <v>10300026002</v>
+        <v>10300026003</v>
       </c>
     </row>
     <row r="1161">
       <c r="A1161">
-        <v>10300027002294</v>
+        <v>10300026002945</v>
       </c>
       <c r="B1161" t="str">
-        <v>هوراند</v>
+        <v>لاریجان</v>
       </c>
       <c r="C1161" t="str">
-        <v>هوراند</v>
+        <v>لاریجان</v>
       </c>
       <c r="D1161">
         <v>103</v>
       </c>
       <c r="E1161">
-        <v>10300027</v>
+        <v>10300026</v>
       </c>
       <c r="F1161">
-        <v>10300027001</v>
+        <v>10300026002</v>
       </c>
     </row>
     <row r="1162">
       <c r="A1162">
-        <v>10300028002296</v>
+        <v>10300027002294</v>
       </c>
       <c r="B1162" t="str">
-        <v>لیلان</v>
+        <v>هوراند</v>
       </c>
       <c r="C1162" t="str">
-        <v>لیلان</v>
+        <v>هوراند</v>
       </c>
       <c r="D1162">
         <v>103</v>
       </c>
       <c r="E1162">
-        <v>10300028</v>
+        <v>10300027</v>
       </c>
       <c r="F1162">
-        <v>10300028001</v>
+        <v>10300027001</v>
       </c>
     </row>
     <row r="1163">
       <c r="A1163">
-        <v>10300029002144</v>
+        <v>10300028002296</v>
       </c>
       <c r="B1163" t="str">
-        <v>ترکمانچای</v>
+        <v>لیلان</v>
       </c>
       <c r="C1163" t="str">
-        <v>ترکمانچای</v>
+        <v>لیلان</v>
       </c>
       <c r="D1163">
         <v>103</v>
       </c>
       <c r="E1163">
-        <v>10300029</v>
+        <v>10300028</v>
       </c>
       <c r="F1163">
-        <v>10300029001</v>
+        <v>10300028001</v>
       </c>
     </row>
     <row r="1164">
@@ -33821,42 +33821,42 @@
     </row>
     <row r="1672">
       <c r="A1672">
-        <v>12900011002624</v>
+        <v>12900011002345</v>
       </c>
       <c r="B1672" t="str">
-        <v>دیهوک</v>
+        <v>عشق آباد</v>
       </c>
       <c r="C1672" t="str">
-        <v>دیهوک</v>
+        <v>عشق-آباد</v>
       </c>
       <c r="D1672">
         <v>129</v>
       </c>
       <c r="E1672">
-        <v>12900011</v>
+        <v>12900012</v>
       </c>
       <c r="F1672">
-        <v>12900011003</v>
+        <v>12900012001</v>
       </c>
     </row>
     <row r="1673">
       <c r="A1673">
-        <v>12900012002345</v>
+        <v>12900011002624</v>
       </c>
       <c r="B1673" t="str">
-        <v>عشق آباد</v>
+        <v>دیهوک</v>
       </c>
       <c r="C1673" t="str">
-        <v>عشق-آباد</v>
+        <v>دیهوک</v>
       </c>
       <c r="D1673">
         <v>129</v>
       </c>
       <c r="E1673">
-        <v>12900012</v>
+        <v>12900011</v>
       </c>
       <c r="F1673">
-        <v>12900012001</v>
+        <v>12900011003</v>
       </c>
     </row>
   </sheetData>
